--- a/test_cases.xlsx
+++ b/test_cases.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" r:id="R4ef4240f0eb04579"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Cases" sheetId="1" r:id="R7281b18563e54fa5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -415,46 +415,72 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="1" t="str">
-        <x:v>Test Case ID</x:v>
-      </x:c>
-      <x:c r="B1" s="1" t="str">
-        <x:v>Module / Function</x:v>
-      </x:c>
-      <x:c r="C1" s="1" t="str">
-        <x:v>Objective</x:v>
-      </x:c>
-      <x:c r="D1" s="1" t="str">
-        <x:v>Input A</x:v>
-      </x:c>
-      <x:c r="E1" s="1" t="str">
-        <x:v>Input B</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="str">
-        <x:v>Technique</x:v>
-      </x:c>
-      <x:c r="G1" s="1" t="str">
-        <x:v>Expected Result</x:v>
-      </x:c>
-      <x:c r="H1" s="1" t="str">
-        <x:v>Actual Result</x:v>
-      </x:c>
-      <x:c r="I1" s="1" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="J1" s="1" t="str">
-        <x:v>Author</x:v>
+      <x:c r="A1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Test Case ID</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Module / Function</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Objective</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Input A</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Input B</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Technique</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Expected Result</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Actual Result</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Status</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Author</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
-      <x:c r="A2" s="2" t="str">
-        <x:v>TC-ADD-01</x:v>
-      </x:c>
-      <x:c r="B2" s="2" t="str">
-        <x:v>addition.add</x:v>
-      </x:c>
-      <x:c r="C2" s="2" t="str">
-        <x:v>Add positive integers</x:v>
+      <x:c r="A2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-ADD-01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">addition.add</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Add positive integers</x:t>
+        </x:is>
       </x:c>
       <x:c r="D2" s="2" t="n">
         <x:v>2</x:v>
@@ -462,341 +488,735 @@
       <x:c r="E2" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F2" s="2" t="str">
-        <x:v>ECP</x:v>
-      </x:c>
-      <x:c r="G2" s="2" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H2" s="2" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I2" s="2" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="J2" s="2" t="str">
-        <x:v>Ahmed</x:v>
+      <x:c r="F2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J2" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ahmed</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
-      <x:c r="A3" s="2" t="str">
-        <x:v>TC-ADD-03</x:v>
-      </x:c>
-      <x:c r="B3" s="2" t="str">
-        <x:v>addition.add</x:v>
-      </x:c>
-      <x:c r="C3" s="2" t="str">
-        <x:v>Add mixed-sign values</x:v>
+      <x:c r="A3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-ADD-02</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">addition.add</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Add zero values</x:t>
+        </x:is>
       </x:c>
       <x:c r="D3" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E3" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I3" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J3" s="2" t="str">
+        <x:v>Abdullah</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-ADD-03</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">addition.add</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Add mixed-sign values</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D4" s="2" t="n">
         <x:v>-2</x:v>
-      </x:c>
-      <x:c r="E3" s="2" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="F3" s="2" t="str">
-        <x:v>ECP</x:v>
-      </x:c>
-      <x:c r="G3" s="2" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="2" t="str">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="I3" s="2" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="J3" s="2" t="str">
-        <x:v>Ahmed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4">
-      <x:c r="A4" s="2" t="str">
-        <x:v>TC-SUB-01</x:v>
-      </x:c>
-      <x:c r="B4" s="2" t="str">
-        <x:v>subtraction.subtract</x:v>
-      </x:c>
-      <x:c r="C4" s="2" t="str">
-        <x:v>Subtract smaller from larger</x:v>
-      </x:c>
-      <x:c r="D4" s="2" t="n">
-        <x:v>8</x:v>
       </x:c>
       <x:c r="E4" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F4" s="2" t="str">
-        <x:v>ECP</x:v>
-      </x:c>
-      <x:c r="G4" s="2" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="H4" s="2" t="str">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="I4" s="2" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="J4" s="2" t="str">
-        <x:v>Ahmed</x:v>
+      <x:c r="F4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">1</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J4" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ahmed</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="5">
-      <x:c r="A5" s="2" t="str">
-        <x:v>TC-SUB-03</x:v>
-      </x:c>
-      <x:c r="B5" s="2" t="str">
-        <x:v>subtraction.subtract</x:v>
-      </x:c>
-      <x:c r="C5" s="2" t="str">
-        <x:v>Subtract same number</x:v>
+      <x:c r="A5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-ADD-04</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">addition.add</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Add decimal values</x:t>
+        </x:is>
       </x:c>
       <x:c r="D5" s="2" t="n">
-        <x:v>7</x:v>
+        <x:v>2.5</x:v>
       </x:c>
       <x:c r="E5" s="2" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F5" s="2" t="str">
-        <x:v>BVA</x:v>
-      </x:c>
-      <x:c r="G5" s="2" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H5" s="2" t="str">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="I5" s="2" t="str">
-        <x:v>Pass</x:v>
+        <x:v>1.5</x:v>
+      </x:c>
+      <x:c r="F5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">4.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I5" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
       </x:c>
       <x:c r="J5" s="2" t="str">
-        <x:v>Ahmed</x:v>
+        <x:v>Abdullah</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="2" t="str">
-        <x:v>TC-MUL-01</x:v>
-      </x:c>
-      <x:c r="B6" s="2" t="str">
-        <x:v>multiplication.multiply</x:v>
-      </x:c>
-      <x:c r="C6" s="2" t="str">
-        <x:v>Multiply positive integers</x:v>
+      <x:c r="A6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-SUB-01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">subtraction.subtract</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Subtract smaller from larger</x:t>
+        </x:is>
       </x:c>
       <x:c r="D6" s="2" t="n">
-        <x:v>2</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E6" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F6" s="2" t="str">
-        <x:v>ECP</x:v>
-      </x:c>
-      <x:c r="G6" s="2" t="str">
+      <x:c r="F6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J6" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ahmed</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-SUB-02</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">subtraction.subtract</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Result is negative</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D7" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="E7" s="2" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I7" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J7" s="2" t="str">
+        <x:v>Abdullah</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-SUB-03</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">subtraction.subtract</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Subtract same number</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D8" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E8" s="2" t="n">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="F8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J8" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ahmed</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-SUB-04</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">subtraction.subtract</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Subtract zero</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D9" s="2" t="n">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E9" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">9</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I9" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J9" s="2" t="str">
+        <x:v>Abdullah</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-MUL-01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">multiplication.multiply</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Multiply positive integers</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D10" s="2" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="E10" s="2" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="F10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J10" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ahmed</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-MUL-02</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">multiplication.multiply</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Multiply by zero</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D11" s="2" t="n">
+        <x:v>999</x:v>
+      </x:c>
+      <x:c r="E11" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I11" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J11" s="2" t="str">
+        <x:v>Abdullah</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-MUL-03</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">multiplication.multiply</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Multiply two negative values</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D12" s="2" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="E12" s="2" t="n">
+        <x:v>-3</x:v>
+      </x:c>
+      <x:c r="F12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">6</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J12" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ahmed</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-MUL-04</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">multiplication.multiply</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Multiply decimal values</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D13" s="2" t="n">
+        <x:v>2.5</x:v>
+      </x:c>
+      <x:c r="E13" s="2" t="n">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="F13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">10.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">10.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I13" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J13" s="2" t="str">
+        <x:v>Abdullah</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-DIV-01</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">division.divide</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Exact division</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D14" s="2" t="n">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="H6" s="2" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I6" s="2" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="J6" s="2" t="str">
-        <x:v>Ahmed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7">
-      <x:c r="A7" s="2" t="str">
-        <x:v>TC-MUL-03</x:v>
-      </x:c>
-      <x:c r="B7" s="2" t="str">
-        <x:v>multiplication.multiply</x:v>
-      </x:c>
-      <x:c r="C7" s="2" t="str">
-        <x:v>Multiply two negative values</x:v>
-      </x:c>
-      <x:c r="D7" s="2" t="n">
-        <x:v>-2</x:v>
-      </x:c>
-      <x:c r="E7" s="2" t="n">
-        <x:v>-3</x:v>
-      </x:c>
-      <x:c r="F7" s="2" t="str">
-        <x:v>ECP</x:v>
-      </x:c>
-      <x:c r="G7" s="2" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="H7" s="2" t="str">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="I7" s="2" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="J7" s="2" t="str">
-        <x:v>Ahmed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8">
-      <x:c r="A8" s="2" t="str">
-        <x:v>TC-DIV-01</x:v>
-      </x:c>
-      <x:c r="B8" s="2" t="str">
-        <x:v>division.divide</x:v>
-      </x:c>
-      <x:c r="C8" s="2" t="str">
-        <x:v>Exact division</x:v>
-      </x:c>
-      <x:c r="D8" s="2" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E8" s="2" t="n">
+      <x:c r="E14" s="2" t="n">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F8" s="2" t="str">
-        <x:v>ECP</x:v>
-      </x:c>
-      <x:c r="G8" s="2" t="str">
+      <x:c r="F14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J14" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ahmed</x:t>
+        </x:is>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-DIV-02</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">division.divide</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Fractional quotient</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D15" s="2" t="n">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E15" s="2" t="n">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="H8" s="2" t="str">
-        <x:v>2.0</x:v>
-      </x:c>
-      <x:c r="I8" s="2" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="J8" s="2" t="str">
-        <x:v>Ahmed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9">
-      <x:c r="A9" s="2" t="str">
-        <x:v>TC-DIV-03</x:v>
-      </x:c>
-      <x:c r="B9" s="2" t="str">
-        <x:v>division.divide</x:v>
-      </x:c>
-      <x:c r="C9" s="2" t="str">
-        <x:v>Divide by one</x:v>
-      </x:c>
-      <x:c r="D9" s="2" t="n">
+      <x:c r="F15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ECP</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">2.5</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I15" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J15" s="2" t="str">
+        <x:v>Abdullah</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-DIV-03</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">division.divide</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Divide by one</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D16" s="2" t="n">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="E9" s="2" t="n">
+      <x:c r="E16" s="2" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="F9" s="2" t="str">
-        <x:v>BVA</x:v>
-      </x:c>
-      <x:c r="G9" s="2" t="str">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="H9" s="2" t="str">
-        <x:v>17.0</x:v>
-      </x:c>
-      <x:c r="I9" s="2" t="str">
-        <x:v>Pass</x:v>
-      </x:c>
-      <x:c r="J9" s="2" t="str">
-        <x:v>Ahmed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10">
-      <x:c r="A10" s="2"/>
-      <x:c r="B10" s="2"/>
-      <x:c r="C10" s="2"/>
-      <x:c r="D10" s="2"/>
-      <x:c r="E10" s="2"/>
-      <x:c r="F10" s="2"/>
-      <x:c r="G10" s="2"/>
-      <x:c r="H10" s="2"/>
-      <x:c r="I10" s="2"/>
-      <x:c r="J10" s="2"/>
-    </x:row>
-    <x:row r="11">
-      <x:c r="A11" s="2"/>
-      <x:c r="B11" s="2"/>
-      <x:c r="C11" s="2"/>
-      <x:c r="D11" s="2"/>
-      <x:c r="E11" s="2"/>
-      <x:c r="F11" s="2"/>
-      <x:c r="G11" s="2"/>
-      <x:c r="H11" s="2"/>
-      <x:c r="I11" s="2"/>
-      <x:c r="J11" s="2"/>
-    </x:row>
-    <x:row r="12">
-      <x:c r="A12" s="2"/>
-      <x:c r="B12" s="2"/>
-      <x:c r="C12" s="2"/>
-      <x:c r="D12" s="2"/>
-      <x:c r="E12" s="2"/>
-      <x:c r="F12" s="2"/>
-      <x:c r="G12" s="2"/>
-      <x:c r="H12" s="2"/>
-      <x:c r="I12" s="2"/>
-      <x:c r="J12" s="2"/>
-    </x:row>
-    <x:row r="13">
-      <x:c r="A13" s="2"/>
-      <x:c r="B13" s="2"/>
-      <x:c r="C13" s="2"/>
-      <x:c r="D13" s="2"/>
-      <x:c r="E13" s="2"/>
-      <x:c r="F13" s="2"/>
-      <x:c r="G13" s="2"/>
-      <x:c r="H13" s="2"/>
-      <x:c r="I13" s="2"/>
-      <x:c r="J13" s="2"/>
-    </x:row>
-    <x:row r="14">
-      <x:c r="A14" s="2"/>
-      <x:c r="B14" s="2"/>
-      <x:c r="C14" s="2"/>
-      <x:c r="D14" s="2"/>
-      <x:c r="E14" s="2"/>
-      <x:c r="F14" s="2"/>
-      <x:c r="G14" s="2"/>
-      <x:c r="H14" s="2"/>
-      <x:c r="I14" s="2"/>
-      <x:c r="J14" s="2"/>
-    </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="2"/>
-      <x:c r="B15" s="2"/>
-      <x:c r="C15" s="2"/>
-      <x:c r="D15" s="2"/>
-      <x:c r="E15" s="2"/>
-      <x:c r="F15" s="2"/>
-      <x:c r="G15" s="2"/>
-      <x:c r="H15" s="2"/>
-      <x:c r="I15" s="2"/>
-      <x:c r="J15" s="2"/>
-    </x:row>
-    <x:row r="16">
-      <x:c r="A16" s="2"/>
-      <x:c r="B16" s="2"/>
-      <x:c r="C16" s="2"/>
-      <x:c r="D16" s="2"/>
-      <x:c r="E16" s="2"/>
-      <x:c r="F16" s="2"/>
-      <x:c r="G16" s="2"/>
-      <x:c r="H16" s="2"/>
-      <x:c r="I16" s="2"/>
-      <x:c r="J16" s="2"/>
+      <x:c r="F16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BVA</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">17</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">17.0</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J16" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Ahmed</x:t>
+        </x:is>
+      </x:c>
     </x:row>
     <x:row r="17">
-      <x:c r="A17" s="2"/>
-      <x:c r="B17" s="2"/>
-      <x:c r="C17" s="2"/>
-      <x:c r="D17" s="2"/>
-      <x:c r="E17" s="2"/>
-      <x:c r="F17" s="2"/>
-      <x:c r="G17" s="2"/>
-      <x:c r="H17" s="2"/>
-      <x:c r="I17" s="2"/>
-      <x:c r="J17" s="2"/>
+      <x:c r="A17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">TC-DIV-04</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="B17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">division.divide</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Divide by zero</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D17" s="2" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="E17" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">BVA / invalid input</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ZeroDivisionError</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ZeroDivisionError</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I17" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Pass</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J17" s="2" t="str">
+        <x:v>Abdullah</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
